--- a/docs/domande.xlsx
+++ b/docs/domande.xlsx
@@ -10,7 +10,7 @@
     <sheet name="domande" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'domande'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'domande'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>livello</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>chi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2664,8 +2670,119 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Qual è il più grande buco di trama della storia?</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cypher entra da solo nel Matrix</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>La vita di Livio</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>I poteri di Imhotep</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Suzaku schiva le pallottole</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Maggi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Qual è il potere più forte del crossverse?</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Il sacchettino di Chrollo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>L'intelligenza di Lelouch</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lo Sharingan di Itachi</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Le mie cazzate ai JudgmentDay</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Meliador</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oggi mi sento istrionico: vediamo la tua fortuna. Trova la mia vera Lisa in mezzo alle altre TR..ragazze.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Livio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G61"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/domande.xlsx
+++ b/docs/domande.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Babidi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
